--- a/diseases/d239/2026-2029.xlsx
+++ b/diseases/d239/2026-2029.xlsx
@@ -6581,12 +6581,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -6611,33 +6611,28 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>0.1027936847111168</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_802_MONTHLY</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6650,7 +6645,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
@@ -6660,55 +6655,55 @@
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_802_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_PNSP_PRE_2025; SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
         </is>
       </c>
       <c r="AT32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -6740,12 +6735,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -6770,38 +6765,38 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_802_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_802_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>PRP-infeksjon/-smittebærertilstand</t>
+          <t>Penicillinresistenta pneumokocker</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -6826,7 +6821,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
@@ -6841,7 +6836,7 @@
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>not_comparable</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
@@ -6861,17 +6856,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_PRP_infection_or_carriage</t>
+          <t>SE_FOHM_SMINET_PRP_from_2025</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>FHI MSIS penicillin-resistant pneumococcal surveillance explicitly includes infection and carriage.</t>
+          <t>Swedish PRP definition effective 2025-01-01; not automatically comparable with the preceding PNSP series.</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -6884,63 +6879,456 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNSP_PRE_2025; SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
+        </is>
+      </c>
+      <c r="AT33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>D239</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>penicillin-non-susceptible-resistant-pneumococcal-surveillance</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Penicillin-non-susceptible/resistant pneumococcal surveillance</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>D239</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Penicillin-non-susceptible/resistant pneumococcal surveillance</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>青霉素敏感性降低或耐药肺炎球菌监测</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_802_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ33" t="inlineStr">
+      <c r="AQ34" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AS33" t="inlineStr">
+      <c r="AS34" t="inlineStr">
         <is>
           <t>SER_NO_FHI_802_MONTHLY</t>
         </is>
       </c>
-      <c r="AT33" t="n">
+      <c r="AT34" t="n">
         <v>1</v>
       </c>
-      <c r="AU33" t="inlineStr">
+      <c r="AU34" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV33" t="inlineStr">
+      <c r="AV34" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW33" t="inlineStr">
+      <c r="AW34" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
+      <c r="AX34" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr">
+      <c r="AY34" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
+      <c r="AZ34" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA33" t="inlineStr">
+      <c r="BA34" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB33" t="inlineStr">
+      <c r="BB34" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC33" t="inlineStr">
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>D239</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>penicillin-non-susceptible-resistant-pneumococcal-surveillance</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Penicillin-non-susceptible/resistant pneumococcal surveillance</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>D239</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Penicillin-non-susceptible/resistant pneumococcal surveillance</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>青霉素敏感性降低或耐药肺炎球菌监测</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_802_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_802_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>PRP-infeksjon/-smittebærertilstand</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_PRP_infection_or_carriage</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>FHI MSIS penicillin-resistant pneumococcal surveillance explicitly includes infection and carriage.</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_802_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV35" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA35" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC35" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -7062,7 +7450,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -7072,7 +7460,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11">
@@ -7092,7 +7480,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -7124,7 +7512,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>171</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d239/2026-2029.xlsx
+++ b/diseases/d239/2026-2029.xlsx
@@ -6227,13 +6227,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -6386,10 +6386,10 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -7008,13 +7008,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -7167,10 +7167,10 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d239/2026-2029.xlsx
+++ b/diseases/d239/2026-2029.xlsx
@@ -7008,13 +7008,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R34" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -7167,10 +7167,10 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d239/2026-2029.xlsx
+++ b/diseases/d239/2026-2029.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7008,13 +7008,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.07075903303182025</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -7167,10 +7167,10 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d239/2026-2029.xlsx
+++ b/diseases/d239/2026-2029.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6227,13 +6227,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.05306927477386519</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -6386,10 +6386,10 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7329,6 +7329,787 @@
         </is>
       </c>
       <c r="BC35" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>D239</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>penicillin-non-susceptible-resistant-pneumococcal-surveillance</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Penicillin-non-susceptible/resistant pneumococcal surveillance</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>D239</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Penicillin-non-susceptible/resistant pneumococcal surveillance</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>青霉素敏感性降低或耐药肺炎球菌监测</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>19</v>
+      </c>
+      <c r="O36" t="n">
+        <v>19</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.1775527281373836</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNSP_PRE_2025; SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
+        </is>
+      </c>
+      <c r="AT36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV36" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA36" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>D239</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>penicillin-non-susceptible-resistant-pneumococcal-surveillance</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Penicillin-non-susceptible/resistant pneumococcal surveillance</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>D239</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Penicillin-non-susceptible/resistant pneumococcal surveillance</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>青霉素敏感性降低或耐药肺炎球菌监测</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>19</v>
+      </c>
+      <c r="O37" t="n">
+        <v>19</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Penicillinresistenta pneumokocker</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_PRP_from_2025</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Swedish PRP definition effective 2025-01-01; not automatically comparable with the preceding PNSP series.</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PNSP_PRE_2025; SER_SE_FOHM_SMINET_PRP_FROM_2025</t>
+        </is>
+      </c>
+      <c r="AT37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV37" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>D239</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>penicillin-non-susceptible-resistant-pneumococcal-surveillance</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Penicillin-non-susceptible/resistant pneumococcal surveillance</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>D239</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Penicillin-non-susceptible/resistant pneumococcal surveillance</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>青霉素敏感性降低或耐药肺炎球菌监测</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_802_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_802_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA38" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>D239</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>penicillin-non-susceptible-resistant-pneumococcal-surveillance</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Penicillin-non-susceptible/resistant pneumococcal surveillance</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>D239</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Penicillin-non-susceptible/resistant pneumococcal surveillance</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>青霉素敏感性降低或耐药肺炎球菌监测</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_802_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_802_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>PRP-infeksjon/-smittebærertilstand</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_PRP_infection_or_carriage</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>FHI MSIS penicillin-resistant pneumococcal surveillance explicitly includes infection and carriage.</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_802_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV39" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA39" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC39" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -7367,7 +8148,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -7450,7 +8231,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -7460,7 +8241,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
@@ -7480,7 +8261,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -7512,7 +8293,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>187</v>
+        <v>208</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d239/2026-2029.xlsx
+++ b/diseases/d239/2026-2029.xlsx
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O36" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R36" t="n">
-        <v>0.1775527281373836</v>
+        <v>0.1682078477091002</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -7555,10 +7555,10 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O37" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d239/2026-2029.xlsx
+++ b/diseases/d239/2026-2029.xlsx
@@ -4277,13 +4277,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2055873694222336</v>
+        <v>0.1962424889939503</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -5058,13 +5058,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R24" t="n">
-        <v>0.214932249850517</v>
+        <v>0.2055873694222336</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -5212,10 +5212,10 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -8293,7 +8293,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d239/2026-2029.xlsx
+++ b/diseases/d239/2026-2029.xlsx
@@ -30001,13 +30001,13 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R209" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="U209" t="inlineStr">
         <is>
@@ -30256,7 +30256,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="16">
